--- a/饮料可比公司研究/data/饮料可比公司_横向对比数据表_第一版.xlsx
+++ b/饮料可比公司研究/data/饮料可比公司_横向对比数据表_第一版.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR3"/>
+  <dimension ref="A1:AR23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,12 +646,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>605499.SH</t>
+          <t>000848.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>东鹏饮料</t>
+          <t>承德露露</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -663,124 +663,124 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15838851828.27</v>
+        <v>3287292242.27</v>
       </c>
       <c r="G2" t="n">
-        <v>8741561002.65</v>
+        <v>1941394035.54</v>
       </c>
       <c r="H2" t="n">
-        <v>7097290825.620001</v>
+        <v>1345898206.73</v>
       </c>
       <c r="I2" t="n">
-        <v>2681079787.33</v>
+        <v>418383805.7</v>
       </c>
       <c r="J2" t="n">
-        <v>425653777.87</v>
+        <v>55365343.77</v>
       </c>
       <c r="K2" t="n">
-        <v>62671297.9</v>
+        <v>15783776.88</v>
       </c>
       <c r="L2" t="n">
-        <v>-190535731.5</v>
+        <v>-51704612.59</v>
       </c>
       <c r="M2" t="n">
-        <v>4144770035.72</v>
+        <v>879829678.58</v>
       </c>
       <c r="N2" t="n">
-        <v>4107312298.7</v>
+        <v>880065353.1599998</v>
       </c>
       <c r="O2" t="n">
-        <v>3326708852.44</v>
+        <v>666239411.22</v>
       </c>
       <c r="P2" t="n">
-        <v>5789408508.54</v>
+        <v>630404373.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1687480710.01</v>
+        <v>215067739.84</v>
       </c>
       <c r="R2" t="n">
-        <v>5652549123.16</v>
+        <v>3390023990.57</v>
       </c>
       <c r="S2" t="n">
-        <v>1068083706.94</v>
+        <v>192501283.44</v>
       </c>
       <c r="T2" t="n">
-        <v>12705623457.77</v>
+        <v>3611459651.07</v>
       </c>
       <c r="U2" t="n">
-        <v>3669663003.83</v>
+        <v>560296081.14</v>
       </c>
       <c r="V2" t="n">
-        <v>746119457.72</v>
+        <v>297895836.92</v>
       </c>
       <c r="W2" t="n">
-        <v>22676296132.9</v>
+        <v>4591344198.86</v>
       </c>
       <c r="X2" t="n">
-        <v>6551336921.28</v>
+        <v>5600000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>133500000</v>
       </c>
       <c r="Z2" t="n">
-        <v>14845041765.22</v>
+        <v>963689198.6900001</v>
       </c>
       <c r="AA2" t="n">
-        <v>14984716162.9</v>
+        <v>963689198.6900001</v>
       </c>
       <c r="AB2" t="n">
-        <v>7687803337.75</v>
+        <v>3438855446.69</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4480937698370528</v>
+        <v>0.4094245682</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2100347227506932</v>
+        <v>0.2026711841</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.169272357390494</v>
+        <v>0.1272730791</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.026874029916125</v>
+        <v>0.0168422336</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0039568081436396</v>
+        <v>0.0048014523</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.0120296429037818</v>
+        <v>-0.0157286328</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2001031954502587</v>
+        <v>0.148916765</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1779638399743635</v>
+        <v>0.1518912717</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4748519894750163</v>
+        <v>0.2041302429</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.6608096875732435</v>
+        <v>0.2098926059</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8558833082933874</v>
+        <v>3.7475356743</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.3807701731364061</v>
+        <v>3.5177565497</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.74028109021134</v>
+        <v>0.9462129728999999</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1065405957645299</v>
+        <v>0.0654239794</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>年度报告</t>
+          <t>2024年年度报告</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>E:\Codex\investment\东鹏饮料研究\raw\official\2024年年度报告.pdf</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_000848.SZ_承德露露_2024_年报全文.pdf</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>605499.SH</t>
+          <t>000848.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>东鹏饮料</t>
+          <t>承德露露</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -809,122 +809,3042 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1955912695.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1063626068.99</v>
+      </c>
+      <c r="H3" t="n">
+        <v>892286626.0499998</v>
+      </c>
+      <c r="I3" t="n">
+        <v>365404988.08</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39701506.07</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6469744</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-26060545.02</v>
+      </c>
+      <c r="M3" t="n">
+        <v>492118218.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>492257893.34</v>
+      </c>
+      <c r="O3" t="n">
+        <v>383602023.57</v>
+      </c>
+      <c r="P3" t="n">
+        <v>237166894.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>117596423.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3505240095.33</v>
+      </c>
+      <c r="S3" t="n">
+        <v>169506903.83</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3701978535.16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>579307181.89</v>
+      </c>
+      <c r="V3" t="n">
+        <v>295951448.27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4717671367.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>26600000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>420900000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>683803591.08</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>683803591.08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3517503802.35</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.4561996189</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1961243079</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1868207047</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0202981995</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0033077877</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.0133239817</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.2104266919</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.0824151643</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.1102881579</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1449451515</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5.4138038809</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5.1260919671</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.6182628869</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.0601235545</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2025年第三季度报告</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_000848.SZ_承德露露_2025_Q3_季度报告.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>300997.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>欢乐家</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1854775974.79</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1224144451.03</v>
+      </c>
+      <c r="H4" t="n">
+        <v>630631523.76</v>
+      </c>
+      <c r="I4" t="n">
+        <v>292758834.48</v>
+      </c>
+      <c r="J4" t="n">
+        <v>136202576.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4802225.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2976248.56</v>
+      </c>
+      <c r="M4" t="n">
+        <v>199054093.28</v>
+      </c>
+      <c r="N4" t="n">
+        <v>197220719.57</v>
+      </c>
+      <c r="O4" t="n">
+        <v>147380329.57</v>
+      </c>
+      <c r="P4" t="n">
+        <v>60260140.15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>101161063.16</v>
+      </c>
+      <c r="R4" t="n">
+        <v>657343187.73</v>
+      </c>
+      <c r="S4" t="n">
+        <v>252336225.01</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1104954678.74</v>
+      </c>
+      <c r="U4" t="n">
+        <v>664000196.03</v>
+      </c>
+      <c r="V4" t="n">
+        <v>159144581.65</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2054739278.33</v>
+      </c>
+      <c r="X4" t="n">
+        <v>214315648.38</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>32983990.87</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>874465145.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>874465145.88</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1134105074.17</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3400041473</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.0794599087</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1578405362</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0734334381</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0025891134</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0016046405</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2338630878</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.0688430877</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1126074298</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.4255844793</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.263577724</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.7517088483</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.4088750536</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.0545408527</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>2024年年度报告</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_300997.SZ_欢乐家_2024_年报全文.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300997.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>欢乐家</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1500390760.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1056489002.25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>443901758.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>218025454.08</v>
+      </c>
+      <c r="J5" t="n">
+        <v>130911358.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2240667.75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6824166.27</v>
+      </c>
+      <c r="M5" t="n">
+        <v>66541704.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>64947357.39</v>
+      </c>
+      <c r="O5" t="n">
+        <v>44174613.79</v>
+      </c>
+      <c r="P5" t="n">
+        <v>88493838.37999998</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>82491825.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>529455299.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>238679035.38</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1012252533.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>651682762.59</v>
+      </c>
+      <c r="V5" t="n">
+        <v>159014603.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1926813907.86</v>
+      </c>
+      <c r="X5" t="n">
+        <v>300331495.71</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>45542518.03</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>819867480.61</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>819867480.61</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1045468370.46</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.2958574326</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.0294420727</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1453124478</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0872515096</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0014933895</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0045482593</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.2340573468</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.0221896389</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.0405351</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.4255042364</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.2346538402</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.6457815586</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2.0032736178</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.0549802276</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>2025年年度报告</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_300997.SZ_欢乐家_2025_年报全文.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>603156.SH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>养元饮品</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6057544892.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3238814226.46</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2818730665.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>712470607.36</v>
+      </c>
+      <c r="J6" t="n">
+        <v>74725102.59</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44042796.56</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-64190138.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2215181609.85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2205250021.27</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1721987800.29</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1430816867.96</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>37770802.67</v>
+      </c>
+      <c r="R6" t="n">
+        <v>917813668.2600001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>767229903.27</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8064950394.979999</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1068850208.37</v>
+      </c>
+      <c r="V6" t="n">
+        <v>133461567.69</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13824669774.17</v>
+      </c>
+      <c r="X6" t="n">
+        <v>877000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>86240980.15000001</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3678584163.48</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3678584163.48</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10012801967.47</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.4653255925</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.2842715706</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1176170577</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0123358727</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0072707338</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.0105967252</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1372236643</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.1150063578</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.1634898191</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.266088393</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2.1924061097</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.249501881</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.8309099912</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.0062353319</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>2024年年度报告</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_603156.SH_养元饮品_2024_年报全文.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>603156.SH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>养元饮品</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3905326394.37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2164809816.47</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1740516577.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>478379354.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>65493298.49</v>
+      </c>
+      <c r="K7" t="n">
+        <v>31934637.92</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-28310322.73</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1418722265.57</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1414644396.59</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1119043318.87</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-165004678.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>34375704.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>620889966.14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>425521714.36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5393776506.69</v>
+      </c>
+      <c r="U7" t="n">
+        <v>999390432.37</v>
+      </c>
+      <c r="V7" t="n">
+        <v>131335356.12</v>
+      </c>
+      <c r="W7" t="n">
+        <v>11318343947.52</v>
+      </c>
+      <c r="X7" t="n">
+        <v>510000000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>90656867.09999999</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2191730447.11</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2191730447.11</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8988583920.149998</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.4456776213</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.2865428407</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1224940776</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0167702496</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0081772007</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.0072491566</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1474415279</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.08901425509999999</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.1177854421</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1936440929</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2.4609670928</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.283287558</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.1474515563</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.0088022616</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>2025年第三季度报告</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_603156.SH_养元饮品_2025_Q3_季度报告.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>603711.SH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>香飘飘</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3287298269.99</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2027064271.17</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1260233998.82</v>
+      </c>
+      <c r="I8" t="n">
+        <v>761262564.22</v>
+      </c>
+      <c r="J8" t="n">
+        <v>223627843.56</v>
+      </c>
+      <c r="K8" t="n">
+        <v>37185446.18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-59521123.14</v>
+      </c>
+      <c r="M8" t="n">
+        <v>309983809.93</v>
+      </c>
+      <c r="N8" t="n">
+        <v>307306510.16</v>
+      </c>
+      <c r="O8" t="n">
+        <v>253191562.27</v>
+      </c>
+      <c r="P8" t="n">
+        <v>264978950.59</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>57078462.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2485493953.9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>186184656.97</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2995034807.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1342603410.46</v>
+      </c>
+      <c r="V8" t="n">
+        <v>177036102.74</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4873264401.95</v>
+      </c>
+      <c r="X8" t="n">
+        <v>674000000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1043332.31</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1292349484.46</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1292349484.46</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3494451049.87</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3833646646</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.077021171</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2315769674</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.068027853</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0113118565</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.0181063957</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.3109166769</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.0500937521</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.07399104619999999</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2651917437</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2.317511512</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.923236697</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.0465552178</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.0173633353</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>2024年年度报告</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_603711.SH_香飘飘_2024_年报全文.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>603711.SH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>香飘飘</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1683873554.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1129738126.06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>554135428.3400002</v>
+      </c>
+      <c r="I9" t="n">
+        <v>499899198.54</v>
+      </c>
+      <c r="J9" t="n">
+        <v>154656687.02</v>
+      </c>
+      <c r="K9" t="n">
+        <v>43735699.42</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-16489960.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-113809454.87</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-118500015.21</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-89207185.31999998</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-26957483.01</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>70886516.36</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2102621932.43</v>
+      </c>
+      <c r="S9" t="n">
+        <v>184263569.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2834950485.87</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1254263942.34</v>
+      </c>
+      <c r="V9" t="n">
+        <v>174964033.13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4722809658.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>754200000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1043332.31</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1345178960.64</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1345178960.64</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3302659545.38</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.3290837527</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.0529773658</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2968745469</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0918457842</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0259732682</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.009792873400000001</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4146935993</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.0185924337</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.0262485608</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2848259951</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2.1074894634</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.5630797046</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.3021895928</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0420972918</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>2025年第三季度报告</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_603711.SH_香飘飘_2025_Q3_季度报告.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>605337.SH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>李子园</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1415072375.68</v>
+      </c>
+      <c r="G10" t="n">
+        <v>862005362.85</v>
+      </c>
+      <c r="H10" t="n">
+        <v>553067012.83</v>
+      </c>
+      <c r="I10" t="n">
+        <v>201355748.78</v>
+      </c>
+      <c r="J10" t="n">
+        <v>85903884.20999998</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19622844.72</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-3629362.07</v>
+      </c>
+      <c r="M10" t="n">
+        <v>292693902.31</v>
+      </c>
+      <c r="N10" t="n">
+        <v>286825513.91</v>
+      </c>
+      <c r="O10" t="n">
+        <v>223803666.91</v>
+      </c>
+      <c r="P10" t="n">
+        <v>360408945.85</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>139763827.92</v>
+      </c>
+      <c r="R10" t="n">
+        <v>624767417.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>186838923.88</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1150110736.71</v>
+      </c>
+      <c r="U10" t="n">
+        <v>975494985.1900001</v>
+      </c>
+      <c r="V10" t="n">
+        <v>131930361.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2988138207.19</v>
+      </c>
+      <c r="X10" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>588646215.73</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>585226798.1900001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>585226798.1900001</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1729944512.67</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.3908400887</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1581570461</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1422936044</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.0607063537</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.0138670255</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.002564789</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2168669836</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.07402488760000001</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.1302941128</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1958499767</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.9652393572</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.0675646085</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.6103799854</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.0987679714</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>2024年年度报告</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_605337.SH_李子园_2024_年报全文.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>605337.SH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>李子园</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>973407177.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>590358652.21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>383048525.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>150459467.59</v>
+      </c>
+      <c r="J11" t="n">
+        <v>65489806.32</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11435309.34</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1366316.45</v>
+      </c>
+      <c r="M11" t="n">
+        <v>183108593.56</v>
+      </c>
+      <c r="N11" t="n">
+        <v>185963681.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>147915118.42</v>
+      </c>
+      <c r="P11" t="n">
+        <v>316967669.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>173512180.42</v>
+      </c>
+      <c r="R11" t="n">
+        <v>581259051.02</v>
+      </c>
+      <c r="S11" t="n">
+        <v>174851900.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1250670646.57</v>
+      </c>
+      <c r="U11" t="n">
+        <v>906029596.37</v>
+      </c>
+      <c r="V11" t="n">
+        <v>154307828.04</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3199891312.26</v>
+      </c>
+      <c r="X11" t="n">
+        <v>218029861.11</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>603006430.64</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>888300381.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>888300381.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1598441506.49</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3935131505</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.151956059</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.154569918</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.0672789433</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.0117477142</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.0014036433</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.2335965756</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.0478068561</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.0888809877</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.277603298</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.407936631</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.6543496581</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.1429024483</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1782524153</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>2025年第三季度报告</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\A股_605337.SH_李子园_2025_Q3_季度报告.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>605499.SH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>东鹏饮料</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>15838851828.27</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8741561002.65</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7097290825.620001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2681079787.33</v>
+      </c>
+      <c r="J12" t="n">
+        <v>425653777.87</v>
+      </c>
+      <c r="K12" t="n">
+        <v>62671297.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-190535731.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4144770035.72</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4107312298.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3326708852.44</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5789408508.54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1687480710.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5652549123.16</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1068083706.94</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12705623457.77</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3669663003.83</v>
+      </c>
+      <c r="V12" t="n">
+        <v>746119457.72</v>
+      </c>
+      <c r="W12" t="n">
+        <v>22676296132.9</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6551336921.28</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14845041765.22</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>14984716162.9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7687803337.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.4480937698370528</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.2100347227506932</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.169272357390494</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.026874029916125</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.0039568081436396</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.0120296429037818</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.2001031954502587</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.1779638399743635</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.4748519894750163</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.6608096875732435</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.8558833082933874</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.3807701731364061</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.74028109021134</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.1065405957645299</v>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>年度报告</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>E:\Codex\investment\东鹏饮料研究\raw\official\2024年年度报告.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>605499.SH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>东鹏饮料</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>20866019000</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G13" t="n">
         <v>11657729000</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H13" t="n">
         <v>9208290000</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I13" t="n">
         <v>3404838000</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J13" t="n">
         <v>632514000</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K13" t="n">
         <v>66338000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L13" t="n">
         <v>101132000</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M13" t="n">
         <v>5584357000</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N13" t="n">
         <v>5584357000</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O13" t="n">
         <v>4415263000</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P13" t="n">
         <v>6174243000</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q13" t="n">
         <v>2266157000</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R13" t="n">
         <v>2740733000</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S13" t="n">
         <v>656963000</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T13" t="n">
         <v>15387480000</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U13" t="n">
         <v>6456032000</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V13" t="n">
         <v>12262000</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W13" t="n">
         <v>26720736000</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X13" t="n">
         <v>6630230000</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
         <v>16810062000</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA13" t="n">
         <v>17296938000</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AB13" t="n">
         <v>9420959000</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC13" t="n">
         <v>0.4413055504262696</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD13" t="n">
         <v>0.2116006412147904</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE13" t="n">
         <v>0.1631762148783627</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF13" t="n">
         <v>0.0303131133926409</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG13" t="n">
         <v>0.0031792360583971</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH13" t="n">
         <v>0.0048467319041547</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI13" t="n">
         <v>0.1966685643294008</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AJ13" t="n">
         <v>0.1787663270182296</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK13" t="n">
         <v>0.5161405498348466</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL13" t="n">
         <v>0.6473226635673508</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AM13" t="n">
         <v>0.9153731854171626</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN13" t="n">
         <v>0.1630412190032374</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO13" t="n">
         <v>1.398386234296802</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AP13" t="n">
         <v>0.1086051440861814</v>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>年度报告/HKEX年报</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AR13" t="inlineStr">
         <is>
           <t>E:\Codex\investment\东鹏饮料研究\raw\official\2025年度业绩公告_HKEX_2026-03-30.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CELH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Celsius Holdings</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1355630000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>675423000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>680207000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>523479000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-39322000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>155728000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>195050000</v>
+      </c>
+      <c r="O14" t="n">
+        <v>107457000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>262898000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>23390000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>890190000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>131165000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1324580000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>55602000</v>
+      </c>
+      <c r="V14" t="n">
+        <v>12213000</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1766881000</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>365535000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>542464000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>399929000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.5017644932614357</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.0792672041781312</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.3861518260882394</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0007376644069547</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.0290064398102727</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.3868894904951941</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.0608173385757161</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.2686901925091703</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.307017846702749</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>3.623674887493674</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.435307152529853</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.446541407260578</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0172539704786704</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176625000024/celh-20241231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CELH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Celsius Holdings</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2515269000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1247936000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1267333000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1123871000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>16029000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>141062000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>125033000</v>
+      </c>
+      <c r="O15" t="n">
+        <v>63837000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>359442000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>36067000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>398866000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>337698000</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1811154000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>87910000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>111910000</v>
+      </c>
+      <c r="W15" t="n">
+        <v>5119621000</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>669926000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1078726000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2178179000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1181467000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.5038558500104761</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.0253797903922005</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.4468194057971533</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0009541722972770999</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.0063726782304397</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.4477735780944304</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.0124690870671872</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.0540319788872647</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.4254570797330505</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.678975013117325</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.369756546147956</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>5.630621739743409</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.0143392217691229</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176626000024/celh-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Keurig Dr Pepper</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>15351000000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6822000000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8529000000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5013000000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>677000000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2591000000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1914000000</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1441000000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2219000000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>563000000</v>
+      </c>
+      <c r="R16" t="n">
+        <v>510000000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1299000000</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3997000000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2964000000</v>
+      </c>
+      <c r="V16" t="n">
+        <v>23634000000</v>
+      </c>
+      <c r="W16" t="n">
+        <v>53430000000</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1026000000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12912000000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8087000000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>29187000000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>24243000000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5555989837795583</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.0938701061820076</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.3265585303888997</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.0045599635202918</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.0441013614748224</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.3311184939091915</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.0269698671158525</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.0594398383038402</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.5462661426165076</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.4942500309138123</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.0630641770743168</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.539902845246357</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.0366751351703472</v>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813525000013/kdp-20241231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Keurig Dr Pepper</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>16603000000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7604000000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8999000000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5351000000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>888000000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3575000000</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2687000000</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2079000000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1991000000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1026000000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1733000000</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5266000000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3230000000</v>
+      </c>
+      <c r="V17" t="n">
+        <v>23725000000</v>
+      </c>
+      <c r="W17" t="n">
+        <v>55459000000</v>
+      </c>
+      <c r="X17" t="n">
+        <v>895000000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13036000000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8290000000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>29943000000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25516000000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.5420104800337289</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.1252183340360176</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.3222911522014093</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.0042161055230982</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.0534843100644461</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.3265072577245076</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.0374871526713428</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.0814782881329362</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.539912367695054</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.6352231604342582</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.1237635705669481</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.9576719576719576</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.029271818346082</v>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813526000016/kdp-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>47061000000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18324000000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>28737000000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14582000000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-3094000000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9992000000</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13086000000</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10631000000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6805000000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2064000000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>10828000000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4728000000</v>
+      </c>
+      <c r="T18" t="n">
+        <v>25997000000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>100549000000</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>25249000000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>75693000000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24856000000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.6106330082233696</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.225898302203523</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.3098531692909202</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.0657444593187565</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.3098531692909202</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.1057295447990532</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.4277035725780496</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.7527971436811902</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.029624935641015</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.4288486672739514</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.640109114852789</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.0438579715688149</v>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/21344/000002134425000011/ko-20241231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>47941000000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>18397000000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>29544000000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>14521000000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-2236000000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>13762000000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>15998000000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>13107000000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7408000000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2112000000</v>
+      </c>
+      <c r="R19" t="n">
+        <v>10270000000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4425000000</v>
+      </c>
+      <c r="T19" t="n">
+        <v>31044000000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9613000000</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>104816000000</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>21281000000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>72647000000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>32169000000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.6162574831563797</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.2733985523873094</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.302893139483949</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.0466406624809661</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.302893139483949</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.1250477026408182</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.4074419472162641</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.6930907495038925</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.458766035430666</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.4825901038485033</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.5651941710536355</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.0440541498925762</v>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/21344/000162828026010047/ko-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Monster Beverage</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>7492709000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3443831000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4048878000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2118584000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-59165000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1930294000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1989459000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1509048000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1928533000</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>264074000</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1533287000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>737107000</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3641504000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1047024000</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1414252000</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7719089000</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>373951000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1097519000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1761371000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5957718000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.54037571724726</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.2014021897820935</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.2827527400303415</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-0.0078963429648742</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.2827527400303415</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.1954956083548201</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.2532929554571062</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.2281837921547478</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>3.317941648390597</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.397048251556465</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.277979891958374</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.0352441286589403</v>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/865752/000141057825000248/mnst-20241231x10k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Monster Beverage</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>8294343000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3662148000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4632195000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2212841000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-63175000</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2419354000</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2482529000</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1905432000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2098177000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>132275000</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2088117000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>799623000</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5361084000</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1081544000</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1379268000</v>
+      </c>
+      <c r="W21" t="n">
+        <v>9988945000</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>373951000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1447780000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1734837000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8254108000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.5584764218214752</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.2297266944470466</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.2667891839052231</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.0076166370259826</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.2667891839052231</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.1907540786339298</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.230846506975678</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.1736756984846748</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>3.702968683087209</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.442288883670171</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.101155538481562</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.0159476163452608</v>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/865752/000110465926020831/mnst-20251231x10k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>91854000000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>41744000000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50110000000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>37190000000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>813000000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>941000000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12887000000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11946000000</v>
+      </c>
+      <c r="O22" t="n">
+        <v>9578000000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12507000000</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8505000000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5306000000</v>
+      </c>
+      <c r="T22" t="n">
+        <v>25826000000</v>
+      </c>
+      <c r="U22" t="n">
+        <v>28008000000</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1102000000</v>
+      </c>
+      <c r="W22" t="n">
+        <v>99467000000</v>
+      </c>
+      <c r="X22" t="n">
+        <v>7082000000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>37224000000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>31536000000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>81296000000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>18041000000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.5455396607659982</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.1042741742330219</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.4048816600256929</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.008851002678163101</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.0102445184749711</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.4137326627038561</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.09629324298511061</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.5309018347098277</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.8173162958569173</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.8189370877727042</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.2696917808219178</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.30580496972228</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/77476/000007747625000007/pep-20241228.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>93925000000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>43066000000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50859000000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>37368000000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>839000000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1254000000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11498000000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10244000000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>8240000000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>12087000000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>9159000000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5845000000</v>
+      </c>
+      <c r="T23" t="n">
+        <v>27949000000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>29905000000</v>
+      </c>
+      <c r="V23" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="W23" t="n">
+        <v>107399000000</v>
+      </c>
+      <c r="X23" t="n">
+        <v>6861000000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>42321000000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32764000000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>86852000000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>20406000000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.541485227575193</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.0877295714665956</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.3978493478839499</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.0089326590364652</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.0133510779877561</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.4067820069204152</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.0767232469576066</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.4038028030971283</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.8086853695099582</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.8530399218654621</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.2795446221462581</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1.466868932038835</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/77476/000007747626000007/pep-20251227.htm</t>
         </is>
       </c>
     </row>

--- a/饮料可比公司研究/data/饮料可比公司_横向对比数据表_第一版.xlsx
+++ b/饮料可比公司研究/data/饮料可比公司_横向对比数据表_第一版.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR23"/>
+  <dimension ref="A1:AR29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2391,17 +2391,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>00220.HK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Celsius Holdings</t>
+          <t>统一企业中国</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2409,145 +2409,145 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1355630000</v>
+        <v>30331512</v>
       </c>
       <c r="G14" t="n">
-        <v>675423000</v>
+        <v>20461844</v>
       </c>
       <c r="H14" t="n">
-        <v>680207000</v>
+        <v>9869668</v>
       </c>
       <c r="I14" t="n">
-        <v>523479000</v>
+        <v>6738417</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1107488</v>
       </c>
       <c r="K14" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-39322000</v>
+        <v>-180485</v>
       </c>
       <c r="M14" t="n">
-        <v>155728000</v>
+        <v>2243905</v>
       </c>
       <c r="N14" t="n">
-        <v>195050000</v>
+        <v>2483774</v>
       </c>
       <c r="O14" t="n">
-        <v>107457000</v>
+        <v>1849119</v>
       </c>
       <c r="P14" t="n">
-        <v>262898000</v>
+        <v>4373264</v>
       </c>
       <c r="Q14" t="n">
-        <v>23390000</v>
+        <v>696880</v>
       </c>
       <c r="R14" t="n">
-        <v>890190000</v>
+        <v>3406856</v>
       </c>
       <c r="S14" t="n">
-        <v>131165000</v>
+        <v>2487076</v>
       </c>
       <c r="T14" t="n">
-        <v>1324580000</v>
+        <v>9108751</v>
       </c>
       <c r="U14" t="n">
-        <v>55602000</v>
+        <v>6044750</v>
       </c>
       <c r="V14" t="n">
-        <v>12213000</v>
+        <v>7486</v>
       </c>
       <c r="W14" t="n">
-        <v>1766881000</v>
+        <v>23376234</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>201264</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>365535000</v>
+        <v>9200845</v>
       </c>
       <c r="AA14" t="n">
-        <v>542464000</v>
+        <v>9977124</v>
       </c>
       <c r="AB14" t="n">
-        <v>399929000</v>
+        <v>13399110</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.5017644932614357</v>
+        <v>0.325393208225162</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0792672041781312</v>
+        <v>0.0609636275303387</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.3861518260882394</v>
+        <v>0.2221589546871253</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>0.0365127857786977</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0007376644069547</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.0290064398102727</v>
+        <v>-0.0059504122313454</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.3868894904951941</v>
+        <v>0.2586717404658231</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0608173385757161</v>
+        <v>0.0812612891649593</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.2686901925091703</v>
+        <v>0.1380893450763208</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.307017846702749</v>
+        <v>0.4268063025036454</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.623674887493674</v>
+        <v>0.9899907019409632</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.435307152529853</v>
+        <v>0.3702764256978571</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.446541407260578</v>
+        <v>2.365052762964417</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0172539704786704</v>
+        <v>0.0229754454707038</v>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2024年年度报告</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176625000024/celh-20241231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_统一企业中国_2024_年度报告_真实.pdf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>00220.HK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Celsius Holdings</t>
+          <t>统一企业中国</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2555,145 +2555,145 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2515269000</v>
+        <v>17086589</v>
       </c>
       <c r="G15" t="n">
-        <v>1247936000</v>
+        <v>11221781</v>
       </c>
       <c r="H15" t="n">
-        <v>1267333000</v>
+        <v>5864808</v>
       </c>
       <c r="I15" t="n">
-        <v>1123871000</v>
+        <v>3772822</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>559162</v>
       </c>
       <c r="K15" t="n">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16029000</v>
+        <v>-119035</v>
       </c>
       <c r="M15" t="n">
-        <v>141062000</v>
+        <v>1648742</v>
       </c>
       <c r="N15" t="n">
-        <v>125033000</v>
+        <v>1778728</v>
       </c>
       <c r="O15" t="n">
-        <v>63837000</v>
+        <v>1286710</v>
       </c>
       <c r="P15" t="n">
-        <v>359442000</v>
+        <v>872009</v>
       </c>
       <c r="Q15" t="n">
-        <v>36067000</v>
+        <v>627836</v>
       </c>
       <c r="R15" t="n">
-        <v>398866000</v>
+        <v>4254079</v>
       </c>
       <c r="S15" t="n">
-        <v>337698000</v>
+        <v>1842888</v>
       </c>
       <c r="T15" t="n">
-        <v>1811154000</v>
+        <v>8921764</v>
       </c>
       <c r="U15" t="n">
-        <v>87910000</v>
+        <v>6168021</v>
       </c>
       <c r="V15" t="n">
-        <v>111910000</v>
+        <v>6968</v>
       </c>
       <c r="W15" t="n">
-        <v>5119621000</v>
+        <v>23119633</v>
       </c>
       <c r="X15" t="n">
-        <v>7000000</v>
+        <v>2204131</v>
       </c>
       <c r="Y15" t="n">
-        <v>669926000</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1078726000</v>
+        <v>9412547</v>
       </c>
       <c r="AA15" t="n">
-        <v>2178179000</v>
+        <v>10283071</v>
       </c>
       <c r="AB15" t="n">
-        <v>1181467000</v>
+        <v>12836562</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5038558500104761</v>
+        <v>0.3432404208938366</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0253797903922005</v>
+        <v>0.0753052584105581</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.4468194057971533</v>
+        <v>0.2208060368280644</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.0327251975218693</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0009541722972770999</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0063726782304397</v>
+        <v>-0.0069665747797878</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.4477735780944304</v>
+        <v>0.2535312343499337</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0124690870671872</v>
+        <v>0.0553472849533056</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0540319788872647</v>
+        <v>0.0980885871724574</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.4254570797330505</v>
+        <v>0.4447765671712868</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.678975013117325</v>
+        <v>0.947858640174652</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.369756546147956</v>
+        <v>0.4519583275387628</v>
       </c>
       <c r="AO15" t="n">
-        <v>5.630621739743409</v>
+        <v>0.6777043778318347</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.0143392217691229</v>
+        <v>0.036744373028461</v>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2025年中期报告</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176626000024/celh-20251231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_统一企业中国_2025_中期报告_真实.pdf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>00506.HK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>中国食品</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2701,145 +2701,145 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>15351000000</v>
+        <v>21491811</v>
       </c>
       <c r="G16" t="n">
-        <v>6822000000</v>
+        <v>13370967</v>
       </c>
       <c r="H16" t="n">
-        <v>8529000000</v>
+        <v>8120844</v>
       </c>
       <c r="I16" t="n">
-        <v>5013000000</v>
+        <v>5871192</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>537598</v>
       </c>
       <c r="K16" t="n">
-        <v>70000000</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>677000000</v>
+        <v>4747</v>
       </c>
       <c r="M16" t="n">
-        <v>2591000000</v>
+        <v>1865899</v>
       </c>
       <c r="N16" t="n">
-        <v>1914000000</v>
+        <v>1866404</v>
       </c>
       <c r="O16" t="n">
-        <v>1441000000</v>
+        <v>860535</v>
       </c>
       <c r="P16" t="n">
-        <v>2219000000</v>
+        <v>2847149</v>
       </c>
       <c r="Q16" t="n">
-        <v>563000000</v>
+        <v>774634</v>
       </c>
       <c r="R16" t="n">
-        <v>510000000</v>
+        <v>4014404</v>
       </c>
       <c r="S16" t="n">
-        <v>1299000000</v>
+        <v>1443480</v>
       </c>
       <c r="T16" t="n">
-        <v>3997000000</v>
+        <v>7273226</v>
       </c>
       <c r="U16" t="n">
-        <v>2964000000</v>
+        <v>5450960</v>
       </c>
       <c r="V16" t="n">
-        <v>23634000000</v>
+        <v>3544591</v>
       </c>
       <c r="W16" t="n">
-        <v>53430000000</v>
+        <v>17598367</v>
       </c>
       <c r="X16" t="n">
-        <v>1026000000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>12912000000</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8087000000</v>
+        <v>7036960</v>
       </c>
       <c r="AA16" t="n">
-        <v>29187000000</v>
+        <v>7400151</v>
       </c>
       <c r="AB16" t="n">
-        <v>24243000000</v>
+        <v>6461978</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5555989837795583</v>
+        <v>0.3778575942250748</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0938701061820076</v>
+        <v>0.0400401343562904</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.3265585303888997</v>
+        <v>0.273182748536175</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.0250140855975329</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0045599635202918</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0441013614748224</v>
+        <v>0.0002208748252997</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.3311184939091915</v>
+        <v>0.2981968341337079</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0269698671158525</v>
+        <v>0.0508831398699632</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0594398383038402</v>
+        <v>0.1379348759077404</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.5462661426165076</v>
+        <v>0.4205021409088695</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4942500309138123</v>
+        <v>1.033575009663264</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0630641770743168</v>
+        <v>0.5704741820331507</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.539902845246357</v>
+        <v>3.308580127478836</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0366751351703472</v>
+        <v>0.0360432166465636</v>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2024年年度报告</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813525000013/kdp-20241231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_中国食品_2024_年度报告.pdf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>00506.HK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>中国食品</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2847,145 +2847,145 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>16603000000</v>
+        <v>12278061</v>
       </c>
       <c r="G17" t="n">
-        <v>7604000000</v>
+        <v>7602388</v>
       </c>
       <c r="H17" t="n">
-        <v>8999000000</v>
+        <v>4675673</v>
       </c>
       <c r="I17" t="n">
-        <v>5351000000</v>
+        <v>3235163</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>211245</v>
       </c>
       <c r="K17" t="n">
-        <v>70000000</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>888000000</v>
+        <v>1822</v>
       </c>
       <c r="M17" t="n">
-        <v>3575000000</v>
+        <v>1356442</v>
       </c>
       <c r="N17" t="n">
-        <v>2687000000</v>
+        <v>1357351</v>
       </c>
       <c r="O17" t="n">
-        <v>2079000000</v>
+        <v>577845</v>
       </c>
       <c r="P17" t="n">
-        <v>1991000000</v>
+        <v>1881448</v>
       </c>
       <c r="Q17" t="n">
-        <v>486000000</v>
+        <v>330845</v>
       </c>
       <c r="R17" t="n">
-        <v>1026000000</v>
+        <v>5046875</v>
       </c>
       <c r="S17" t="n">
-        <v>1733000000</v>
+        <v>971523</v>
       </c>
       <c r="T17" t="n">
-        <v>5266000000</v>
+        <v>8259505</v>
       </c>
       <c r="U17" t="n">
-        <v>3230000000</v>
+        <v>5659578</v>
       </c>
       <c r="V17" t="n">
-        <v>23725000000</v>
+        <v>3552296</v>
       </c>
       <c r="W17" t="n">
-        <v>55459000000</v>
+        <v>18749206</v>
       </c>
       <c r="X17" t="n">
-        <v>895000000</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>13036000000</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8290000000</v>
+        <v>8223245</v>
       </c>
       <c r="AA17" t="n">
-        <v>29943000000</v>
+        <v>8599278</v>
       </c>
       <c r="AB17" t="n">
-        <v>25516000000</v>
+        <v>6611848</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5420104800337289</v>
+        <v>0.3808152606506841</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1252183340360176</v>
+        <v>0.0470632129942993</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.3222911522014093</v>
+        <v>0.2634913607287014</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.0172050782285574</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0042161055230982</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0534843100644461</v>
+        <v>0.0001483947668935</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.3265072577245076</v>
+        <v>0.2806964389572588</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0374871526713428</v>
+        <v>0.0317955204326847</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0814782881329362</v>
+        <v>0.0883972297015426</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.539912367695054</v>
+        <v>0.4586475821962807</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.6352231604342582</v>
+        <v>1.004409451499986</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.1237635705669481</v>
+        <v>0.6137327782402202</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.9576719576719576</v>
+        <v>3.255973487699989</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.029271818346082</v>
+        <v>0.0269460299961044</v>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2025年中期报告</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813526000016/kdp-20251231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_中国食品_2025_中期报告.pdf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>09633.HK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>农夫山泉</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2993,145 +2993,145 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>47061000000</v>
+        <v>42895992</v>
       </c>
       <c r="G18" t="n">
-        <v>18324000000</v>
+        <v>17980277</v>
       </c>
       <c r="H18" t="n">
-        <v>28737000000</v>
+        <v>24915715</v>
       </c>
       <c r="I18" t="n">
-        <v>14582000000</v>
+        <v>9173297</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1962470</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-3094000000</v>
+        <v>91469</v>
       </c>
       <c r="M18" t="n">
-        <v>9992000000</v>
+        <v>15879327</v>
       </c>
       <c r="N18" t="n">
-        <v>13086000000</v>
+        <v>15787858</v>
       </c>
       <c r="O18" t="n">
-        <v>10631000000</v>
+        <v>12123304</v>
       </c>
       <c r="P18" t="n">
-        <v>6805000000</v>
+        <v>11022144</v>
       </c>
       <c r="Q18" t="n">
-        <v>2064000000</v>
+        <v>6460789</v>
       </c>
       <c r="R18" t="n">
-        <v>10828000000</v>
+        <v>10722048</v>
       </c>
       <c r="S18" t="n">
-        <v>4728000000</v>
+        <v>5013047</v>
       </c>
       <c r="T18" t="n">
-        <v>25997000000</v>
+        <v>19071874</v>
       </c>
       <c r="U18" t="n">
-        <v>10303000000</v>
+        <v>21083239</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>71557</v>
       </c>
       <c r="W18" t="n">
-        <v>100549000000</v>
+        <v>53160312</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3625433</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>25249000000</v>
+        <v>19984737</v>
       </c>
       <c r="AA18" t="n">
-        <v>75693000000</v>
+        <v>20873148</v>
       </c>
       <c r="AB18" t="n">
-        <v>24856000000</v>
+        <v>32287164</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.6106330082233696</v>
+        <v>0.580840163342067</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.225898302203523</v>
+        <v>0.2826209031370577</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.3098531692909202</v>
+        <v>0.2138497461487777</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.0457494956638373</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.0657444593187565</v>
+        <v>0.0021323437397134</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.3098531692909202</v>
+        <v>0.259599241812615</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1057295447990532</v>
+        <v>0.2370206676331163</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.4277035725780496</v>
+        <v>0.3984123781515316</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.7527971436811902</v>
+        <v>0.3926453253321764</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.029624935641015</v>
+        <v>0.9543219908272998</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.4288486672739514</v>
+        <v>0.5365118390099405</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.640109114852789</v>
+        <v>0.9091699754456376</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0438579715688149</v>
+        <v>0.1506152136544598</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2024年年度报告</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/21344/000002134425000011/ko-20241231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_农夫山泉_2024_年度报告.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>09633.HK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>农夫山泉</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3139,128 +3139,128 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>47941000000</v>
+        <v>25622201</v>
       </c>
       <c r="G19" t="n">
-        <v>18397000000</v>
+        <v>10165771</v>
       </c>
       <c r="H19" t="n">
-        <v>29544000000</v>
+        <v>15456430</v>
       </c>
       <c r="I19" t="n">
-        <v>14521000000</v>
+        <v>5010696</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1067728</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-2236000000</v>
+        <v>24563</v>
       </c>
       <c r="M19" t="n">
-        <v>13762000000</v>
+        <v>10058139</v>
       </c>
       <c r="N19" t="n">
-        <v>15998000000</v>
+        <v>10033576</v>
       </c>
       <c r="O19" t="n">
-        <v>13107000000</v>
+        <v>7622082</v>
       </c>
       <c r="P19" t="n">
-        <v>7408000000</v>
+        <v>10406067</v>
       </c>
       <c r="Q19" t="n">
-        <v>2112000000</v>
+        <v>3566386</v>
       </c>
       <c r="R19" t="n">
-        <v>10270000000</v>
+        <v>14905813</v>
       </c>
       <c r="S19" t="n">
-        <v>4425000000</v>
+        <v>5104288</v>
       </c>
       <c r="T19" t="n">
-        <v>31044000000</v>
+        <v>26524390</v>
       </c>
       <c r="U19" t="n">
-        <v>9613000000</v>
+        <v>23570284</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>161201</v>
       </c>
       <c r="W19" t="n">
-        <v>104816000000</v>
+        <v>64393869</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4419502</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>21281000000</v>
+        <v>32135476</v>
       </c>
       <c r="AA19" t="n">
-        <v>72647000000</v>
+        <v>33023445</v>
       </c>
       <c r="AB19" t="n">
-        <v>32169000000</v>
+        <v>31370424</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.6162574831563797</v>
+        <v>0.6032436479598299</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2733985523873094</v>
+        <v>0.2974795959176184</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.302893139483949</v>
+        <v>0.1955607170515913</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.0416719859468747</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.0466406624809661</v>
+        <v>0.0009586608113799</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.302893139483949</v>
+        <v>0.237232702998466</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1250477026408182</v>
+        <v>0.1296777696065102</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.4074419472162641</v>
+        <v>0.2394712787421352</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.6930907495038925</v>
+        <v>0.5128352359135309</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.458766035430666</v>
+        <v>0.8253927839749441</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.4825901038485033</v>
+        <v>0.4638429192709017</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.5651941710536355</v>
+        <v>1.365252564850391</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.0440541498925762</v>
+        <v>0.139191242781992</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2025年中期报告</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/21344/000162828026010047/ko-20251231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_农夫山泉_2025_中期报告.pdf</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3272,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Celsius Holdings</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3289,115 +3289,115 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7492709000</v>
+        <v>1355630000</v>
       </c>
       <c r="G20" t="n">
-        <v>3443831000</v>
+        <v>675423000</v>
       </c>
       <c r="H20" t="n">
-        <v>4048878000</v>
+        <v>680207000</v>
       </c>
       <c r="I20" t="n">
-        <v>2118584000</v>
+        <v>523479000</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="L20" t="n">
-        <v>-59165000</v>
+        <v>-39322000</v>
       </c>
       <c r="M20" t="n">
-        <v>1930294000</v>
+        <v>155728000</v>
       </c>
       <c r="N20" t="n">
-        <v>1989459000</v>
+        <v>195050000</v>
       </c>
       <c r="O20" t="n">
-        <v>1509048000</v>
+        <v>107457000</v>
       </c>
       <c r="P20" t="n">
-        <v>1928533000</v>
+        <v>262898000</v>
       </c>
       <c r="Q20" t="n">
-        <v>264074000</v>
+        <v>23390000</v>
       </c>
       <c r="R20" t="n">
-        <v>1533287000</v>
+        <v>890190000</v>
       </c>
       <c r="S20" t="n">
-        <v>737107000</v>
+        <v>131165000</v>
       </c>
       <c r="T20" t="n">
-        <v>3641504000</v>
+        <v>1324580000</v>
       </c>
       <c r="U20" t="n">
-        <v>1047024000</v>
+        <v>55602000</v>
       </c>
       <c r="V20" t="n">
-        <v>1414252000</v>
+        <v>12213000</v>
       </c>
       <c r="W20" t="n">
-        <v>7719089000</v>
+        <v>1766881000</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>373951000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1097519000</v>
+        <v>365535000</v>
       </c>
       <c r="AA20" t="n">
-        <v>1761371000</v>
+        <v>542464000</v>
       </c>
       <c r="AB20" t="n">
-        <v>5957718000</v>
+        <v>399929000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.54037571724726</v>
+        <v>0.5017644932614357</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.2014021897820935</v>
+        <v>0.0792672041781312</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.2827527400303415</v>
+        <v>0.3861518260882394</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.0007376644069547</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.0078963429648742</v>
+        <v>-0.0290064398102727</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.2827527400303415</v>
+        <v>0.3868894904951941</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.1954956083548201</v>
+        <v>0.0608173385757161</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.2532929554571062</v>
+        <v>0.2686901925091703</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.2281837921547478</v>
+        <v>0.307017846702749</v>
       </c>
       <c r="AM20" t="n">
-        <v>3.317941648390597</v>
+        <v>3.623674887493674</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.397048251556465</v>
+        <v>2.435307152529853</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.277979891958374</v>
+        <v>2.446541407260578</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.0352441286589403</v>
+        <v>0.0172539704786704</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/865752/000141057825000248/mnst-20241231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176625000024/celh-20241231.htm</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Celsius Holdings</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3435,115 +3435,115 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8294343000</v>
+        <v>2515269000</v>
       </c>
       <c r="G21" t="n">
-        <v>3662148000</v>
+        <v>1247936000</v>
       </c>
       <c r="H21" t="n">
-        <v>4632195000</v>
+        <v>1267333000</v>
       </c>
       <c r="I21" t="n">
-        <v>2212841000</v>
+        <v>1123871000</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="L21" t="n">
-        <v>-63175000</v>
+        <v>16029000</v>
       </c>
       <c r="M21" t="n">
-        <v>2419354000</v>
+        <v>141062000</v>
       </c>
       <c r="N21" t="n">
-        <v>2482529000</v>
+        <v>125033000</v>
       </c>
       <c r="O21" t="n">
-        <v>1905432000</v>
+        <v>63837000</v>
       </c>
       <c r="P21" t="n">
-        <v>2098177000</v>
+        <v>359442000</v>
       </c>
       <c r="Q21" t="n">
-        <v>132275000</v>
+        <v>36067000</v>
       </c>
       <c r="R21" t="n">
-        <v>2088117000</v>
+        <v>398866000</v>
       </c>
       <c r="S21" t="n">
-        <v>799623000</v>
+        <v>337698000</v>
       </c>
       <c r="T21" t="n">
-        <v>5361084000</v>
+        <v>1811154000</v>
       </c>
       <c r="U21" t="n">
-        <v>1081544000</v>
+        <v>87910000</v>
       </c>
       <c r="V21" t="n">
-        <v>1379268000</v>
+        <v>111910000</v>
       </c>
       <c r="W21" t="n">
-        <v>9988945000</v>
+        <v>5119621000</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="Y21" t="n">
-        <v>373951000</v>
+        <v>669926000</v>
       </c>
       <c r="Z21" t="n">
-        <v>1447780000</v>
+        <v>1078726000</v>
       </c>
       <c r="AA21" t="n">
-        <v>1734837000</v>
+        <v>2178179000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8254108000</v>
+        <v>1181467000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5584764218214752</v>
+        <v>0.5038558500104761</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.2297266944470466</v>
+        <v>0.0253797903922005</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.2667891839052231</v>
+        <v>0.4468194057971533</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.0009541722972770999</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.0076166370259826</v>
+        <v>0.0063726782304397</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.2667891839052231</v>
+        <v>0.4477735780944304</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.1907540786339298</v>
+        <v>0.0124690870671872</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.230846506975678</v>
+        <v>0.0540319788872647</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.1736756984846748</v>
+        <v>0.4254570797330505</v>
       </c>
       <c r="AM21" t="n">
-        <v>3.702968683087209</v>
+        <v>1.678975013117325</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.442288883670171</v>
+        <v>0.369756546147956</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.101155538481562</v>
+        <v>5.630621739743409</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.0159476163452608</v>
+        <v>0.0143392217691229</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/865752/000110465926020831/mnst-20251231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176626000024/celh-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3581,115 +3581,115 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>91854000000</v>
+        <v>15351000000</v>
       </c>
       <c r="G22" t="n">
-        <v>41744000000</v>
+        <v>6822000000</v>
       </c>
       <c r="H22" t="n">
-        <v>50110000000</v>
+        <v>8529000000</v>
       </c>
       <c r="I22" t="n">
-        <v>37190000000</v>
+        <v>5013000000</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>813000000</v>
+        <v>70000000</v>
       </c>
       <c r="L22" t="n">
-        <v>941000000</v>
+        <v>677000000</v>
       </c>
       <c r="M22" t="n">
-        <v>12887000000</v>
+        <v>2591000000</v>
       </c>
       <c r="N22" t="n">
-        <v>11946000000</v>
+        <v>1914000000</v>
       </c>
       <c r="O22" t="n">
-        <v>9578000000</v>
+        <v>1441000000</v>
       </c>
       <c r="P22" t="n">
-        <v>12507000000</v>
+        <v>2219000000</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>563000000</v>
       </c>
       <c r="R22" t="n">
-        <v>8505000000</v>
+        <v>510000000</v>
       </c>
       <c r="S22" t="n">
-        <v>5306000000</v>
+        <v>1299000000</v>
       </c>
       <c r="T22" t="n">
-        <v>25826000000</v>
+        <v>3997000000</v>
       </c>
       <c r="U22" t="n">
-        <v>28008000000</v>
+        <v>2964000000</v>
       </c>
       <c r="V22" t="n">
-        <v>1102000000</v>
+        <v>23634000000</v>
       </c>
       <c r="W22" t="n">
-        <v>99467000000</v>
+        <v>53430000000</v>
       </c>
       <c r="X22" t="n">
-        <v>7082000000</v>
+        <v>1026000000</v>
       </c>
       <c r="Y22" t="n">
-        <v>37224000000</v>
+        <v>12912000000</v>
       </c>
       <c r="Z22" t="n">
-        <v>31536000000</v>
+        <v>8087000000</v>
       </c>
       <c r="AA22" t="n">
-        <v>81296000000</v>
+        <v>29187000000</v>
       </c>
       <c r="AB22" t="n">
-        <v>18041000000</v>
+        <v>24243000000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.5455396607659982</v>
+        <v>0.5555989837795583</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1042741742330219</v>
+        <v>0.0938701061820076</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.4048816600256929</v>
+        <v>0.3265585303888997</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.008851002678163101</v>
+        <v>0.0045599635202918</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.0102445184749711</v>
+        <v>0.0441013614748224</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.4137326627038561</v>
+        <v>0.3311184939091915</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.09629324298511061</v>
+        <v>0.0269698671158525</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.5309018347098277</v>
+        <v>0.0594398383038402</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.8173162958569173</v>
+        <v>0.5462661426165076</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.8189370877727042</v>
+        <v>0.4942500309138123</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.2696917808219178</v>
+        <v>0.0630641770743168</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.30580496972228</v>
+        <v>1.539902845246357</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.0366751351703472</v>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/77476/000007747625000007/pep-20241228.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813525000013/kdp-20241231.htm</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -3727,122 +3727,998 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>16603000000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7604000000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8999000000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5351000000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>888000000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3575000000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2687000000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2079000000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1991000000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1026000000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1733000000</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5266000000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3230000000</v>
+      </c>
+      <c r="V23" t="n">
+        <v>23725000000</v>
+      </c>
+      <c r="W23" t="n">
+        <v>55459000000</v>
+      </c>
+      <c r="X23" t="n">
+        <v>895000000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13036000000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8290000000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>29943000000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>25516000000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.5420104800337289</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.1252183340360176</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.3222911522014093</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.0042161055230982</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.0534843100644461</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.3265072577245076</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.0374871526713428</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.0814782881329362</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.539912367695054</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.6352231604342582</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.1237635705669481</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.9576719576719576</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.029271818346082</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813526000016/kdp-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>47061000000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>18324000000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28737000000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>14582000000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-3094000000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9992000000</v>
+      </c>
+      <c r="N24" t="n">
+        <v>13086000000</v>
+      </c>
+      <c r="O24" t="n">
+        <v>10631000000</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6805000000</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2064000000</v>
+      </c>
+      <c r="R24" t="n">
+        <v>10828000000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4728000000</v>
+      </c>
+      <c r="T24" t="n">
+        <v>25997000000</v>
+      </c>
+      <c r="U24" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>100549000000</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>25249000000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>75693000000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>24856000000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.6106330082233696</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.225898302203523</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.3098531692909202</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.0657444593187565</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.3098531692909202</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.1057295447990532</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.4277035725780496</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.7527971436811902</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.029624935641015</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.4288486672739514</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.640109114852789</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.0438579715688149</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/21344/000002134425000011/ko-20241231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>47941000000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>18397000000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>29544000000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14521000000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2236000000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>13762000000</v>
+      </c>
+      <c r="N25" t="n">
+        <v>15998000000</v>
+      </c>
+      <c r="O25" t="n">
+        <v>13107000000</v>
+      </c>
+      <c r="P25" t="n">
+        <v>7408000000</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2112000000</v>
+      </c>
+      <c r="R25" t="n">
+        <v>10270000000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4425000000</v>
+      </c>
+      <c r="T25" t="n">
+        <v>31044000000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>9613000000</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>104816000000</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>21281000000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>72647000000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>32169000000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.6162574831563797</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.2733985523873094</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.302893139483949</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-0.0466406624809661</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.302893139483949</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.1250477026408182</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.4074419472162641</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.6930907495038925</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.458766035430666</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.4825901038485033</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.5651941710536355</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.0440541498925762</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/21344/000162828026010047/ko-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Monster Beverage</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>7492709000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3443831000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4048878000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2118584000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-59165000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1930294000</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1989459000</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1509048000</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1928533000</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>264074000</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1533287000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>737107000</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3641504000</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1047024000</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1414252000</v>
+      </c>
+      <c r="W26" t="n">
+        <v>7719089000</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>373951000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1097519000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1761371000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>5957718000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.54037571724726</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.2014021897820935</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.2827527400303415</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.0078963429648742</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.2827527400303415</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.1954956083548201</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.2532929554571062</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.2281837921547478</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>3.317941648390597</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.397048251556465</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1.277979891958374</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.0352441286589403</v>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/865752/000141057825000248/mnst-20241231x10k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Monster Beverage</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>8294343000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3662148000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4632195000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2212841000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-63175000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2419354000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2482529000</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1905432000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2098177000</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>132275000</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2088117000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>799623000</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5361084000</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1081544000</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1379268000</v>
+      </c>
+      <c r="W27" t="n">
+        <v>9988945000</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>373951000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1447780000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1734837000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8254108000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.5584764218214752</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.2297266944470466</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.2667891839052231</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.0076166370259826</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.2667891839052231</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.1907540786339298</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.230846506975678</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.1736756984846748</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>3.702968683087209</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.442288883670171</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1.101155538481562</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.0159476163452608</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/865752/000110465926020831/mnst-20251231x10k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>91854000000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>41744000000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50110000000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>37190000000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>813000000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>941000000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>12887000000</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11946000000</v>
+      </c>
+      <c r="O28" t="n">
+        <v>9578000000</v>
+      </c>
+      <c r="P28" t="n">
+        <v>12507000000</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8505000000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5306000000</v>
+      </c>
+      <c r="T28" t="n">
+        <v>25826000000</v>
+      </c>
+      <c r="U28" t="n">
+        <v>28008000000</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1102000000</v>
+      </c>
+      <c r="W28" t="n">
+        <v>99467000000</v>
+      </c>
+      <c r="X28" t="n">
+        <v>7082000000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>37224000000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>31536000000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>81296000000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18041000000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.5455396607659982</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.1042741742330219</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.4048816600256929</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.008851002678163101</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.0102445184749711</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.4137326627038561</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.09629324298511061</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.5309018347098277</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.8173162958569173</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.8189370877727042</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.2696917808219178</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1.30580496972228</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/77476/000007747625000007/pep-20241228.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>93925000000</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G29" t="n">
         <v>43066000000</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H29" t="n">
         <v>50859000000</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I29" t="n">
         <v>37368000000</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>839000000</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L29" t="n">
         <v>1254000000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M29" t="n">
         <v>11498000000</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N29" t="n">
         <v>10244000000</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O29" t="n">
         <v>8240000000</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P29" t="n">
         <v>12087000000</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
         <v>9159000000</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S29" t="n">
         <v>5845000000</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T29" t="n">
         <v>27949000000</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U29" t="n">
         <v>29905000000</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V29" t="n">
         <v>500000000</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W29" t="n">
         <v>107399000000</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X29" t="n">
         <v>6861000000</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y29" t="n">
         <v>42321000000</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z29" t="n">
         <v>32764000000</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA29" t="n">
         <v>86852000000</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB29" t="n">
         <v>20406000000</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC29" t="n">
         <v>0.541485227575193</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD29" t="n">
         <v>0.0877295714665956</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE29" t="n">
         <v>0.3978493478839499</v>
       </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.0089326590364652</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH29" t="n">
         <v>0.0133510779877561</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AI29" t="n">
         <v>0.4067820069204152</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AJ29" t="n">
         <v>0.0767232469576066</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AK29" t="n">
         <v>0.4038028030971283</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AL29" t="n">
         <v>0.8086853695099582</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AM29" t="n">
         <v>0.8530399218654621</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AN29" t="n">
         <v>0.2795446221462581</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AO29" t="n">
         <v>1.466868932038835</v>
       </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AR29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/77476/000007747626000007/pep-20251227.htm</t>
         </is>

--- a/饮料可比公司研究/data/饮料可比公司_横向对比数据表_第一版.xlsx
+++ b/饮料可比公司研究/data/饮料可比公司_横向对比数据表_第一版.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR29"/>
+  <dimension ref="A1:AR31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>00506.HK</t>
+          <t>00322.HK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中国食品</t>
+          <t>康师傅控股</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2705,115 +2705,115 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>21491811</v>
+        <v>80650914</v>
       </c>
       <c r="G16" t="n">
-        <v>13370967</v>
+        <v>53955271</v>
       </c>
       <c r="H16" t="n">
-        <v>8120844</v>
+        <v>26695643</v>
       </c>
       <c r="I16" t="n">
-        <v>5871192</v>
+        <v>18041843</v>
       </c>
       <c r="J16" t="n">
-        <v>537598</v>
+        <v>2827531</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>4747</v>
+        <v>423313</v>
       </c>
       <c r="M16" t="n">
-        <v>1865899</v>
+        <v>6353026</v>
       </c>
       <c r="N16" t="n">
-        <v>1866404</v>
+        <v>6059654</v>
       </c>
       <c r="O16" t="n">
-        <v>860535</v>
+        <v>3734429</v>
       </c>
       <c r="P16" t="n">
-        <v>2847149</v>
+        <v>8264000</v>
       </c>
       <c r="Q16" t="n">
-        <v>774634</v>
+        <v>3626035</v>
       </c>
       <c r="R16" t="n">
-        <v>4014404</v>
+        <v>7519398</v>
       </c>
       <c r="S16" t="n">
-        <v>1443480</v>
+        <v>4015218</v>
       </c>
       <c r="T16" t="n">
-        <v>7273226</v>
+        <v>17985741</v>
       </c>
       <c r="U16" t="n">
-        <v>5450960</v>
+        <v>21521843</v>
       </c>
       <c r="V16" t="n">
-        <v>3544591</v>
+        <v>148800</v>
       </c>
       <c r="W16" t="n">
-        <v>17598367</v>
+        <v>53148855</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>11584561</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1670256</v>
       </c>
       <c r="Z16" t="n">
-        <v>7036960</v>
+        <v>32423225</v>
       </c>
       <c r="AA16" t="n">
-        <v>7400151</v>
+        <v>35533504</v>
       </c>
       <c r="AB16" t="n">
-        <v>6461978</v>
+        <v>14229046</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.3778575942250748</v>
+        <v>0.3310023616099378</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0400401343562904</v>
+        <v>0.0463036165963351</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.273182748536175</v>
+        <v>0.2237028956671216</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0250140855975329</v>
+        <v>0.0350588835236262</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0002208748252997</v>
+        <v>0.0052487067908492</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.2981968341337079</v>
+        <v>0.2587617791907479</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0508831398699632</v>
+        <v>0.0702630551478384</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.1379348759077404</v>
+        <v>0.2655721430184204</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.4205021409088695</v>
+        <v>0.6685657480297553</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.033575009663264</v>
+        <v>0.5547178295804936</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.5704741820331507</v>
+        <v>0.2319139444025077</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.308580127478836</v>
+        <v>2.212921975488086</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0360432166465636</v>
+        <v>0.0449596268679608</v>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_中国食品_2024_年度报告.pdf</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_康师傅控股_2024_年度报告_真实.pdf</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>00506.HK</t>
+          <t>00322.HK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中国食品</t>
+          <t>康师傅控股</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2851,124 +2851,124 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12278061</v>
+        <v>79068022</v>
       </c>
       <c r="G17" t="n">
-        <v>7602388</v>
+        <v>51536318</v>
       </c>
       <c r="H17" t="n">
-        <v>4675673</v>
+        <v>27531704</v>
       </c>
       <c r="I17" t="n">
-        <v>3235163</v>
+        <v>18131687</v>
       </c>
       <c r="J17" t="n">
-        <v>211245</v>
+        <v>2988826</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1822</v>
+        <v>320816</v>
       </c>
       <c r="M17" t="n">
-        <v>1356442</v>
+        <v>7173914</v>
       </c>
       <c r="N17" t="n">
-        <v>1357351</v>
+        <v>6965916</v>
       </c>
       <c r="O17" t="n">
-        <v>577845</v>
+        <v>4500698</v>
       </c>
       <c r="P17" t="n">
-        <v>1881448</v>
+        <v>8202000</v>
       </c>
       <c r="Q17" t="n">
-        <v>330845</v>
+        <v>3088096</v>
       </c>
       <c r="R17" t="n">
-        <v>5046875</v>
+        <v>10796902</v>
       </c>
       <c r="S17" t="n">
-        <v>971523</v>
+        <v>3650354</v>
       </c>
       <c r="T17" t="n">
-        <v>8259505</v>
+        <v>21248430</v>
       </c>
       <c r="U17" t="n">
-        <v>5659578</v>
+        <v>21028894</v>
       </c>
       <c r="V17" t="n">
-        <v>3552296</v>
+        <v>141961</v>
       </c>
       <c r="W17" t="n">
-        <v>18749206</v>
+        <v>54939771</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>9226000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>5796647</v>
       </c>
       <c r="Z17" t="n">
-        <v>8223245</v>
+        <v>29357580</v>
       </c>
       <c r="AA17" t="n">
-        <v>8599278</v>
+        <v>36440563</v>
       </c>
       <c r="AB17" t="n">
-        <v>6611848</v>
+        <v>14980057</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3808152606506841</v>
+        <v>0.3482027664736573</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0470632129942993</v>
+        <v>0.0569218488860136</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.2634913607287014</v>
+        <v>0.2293175741768271</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0172050782285574</v>
+        <v>0.037800692674467</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0001483947668935</v>
+        <v>0.0040574683909507</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2806964389572588</v>
+        <v>0.2671182668512942</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0317955204326847</v>
+        <v>0.0832779204724093</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0883972297015426</v>
+        <v>0.3081709150739753</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.4586475821962807</v>
+        <v>0.6632820329738907</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.004409451499986</v>
+        <v>0.7237800254653143</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.6137327782402202</v>
+        <v>0.3677722073822161</v>
       </c>
       <c r="AO17" t="n">
-        <v>3.255973487699989</v>
+        <v>1.822383994660384</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0269460299961044</v>
+        <v>0.0390561939186995</v>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2025年中期报告</t>
+          <t>2025年度业绩公告</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_中国食品_2025_中期报告.pdf</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_康师傅控股_2025_年度业绩公告.pdf</t>
         </is>
       </c>
     </row>
@@ -2980,12 +2980,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09633.HK</t>
+          <t>00506.HK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>农夫山泉</t>
+          <t>中国食品</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2997,115 +2997,115 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>42895992</v>
+        <v>21491811</v>
       </c>
       <c r="G18" t="n">
-        <v>17980277</v>
+        <v>13370967</v>
       </c>
       <c r="H18" t="n">
-        <v>24915715</v>
+        <v>8120844</v>
       </c>
       <c r="I18" t="n">
-        <v>9173297</v>
+        <v>5871192</v>
       </c>
       <c r="J18" t="n">
-        <v>1962470</v>
+        <v>537598</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>91469</v>
+        <v>4747</v>
       </c>
       <c r="M18" t="n">
-        <v>15879327</v>
+        <v>1865899</v>
       </c>
       <c r="N18" t="n">
-        <v>15787858</v>
+        <v>1866404</v>
       </c>
       <c r="O18" t="n">
-        <v>12123304</v>
+        <v>860535</v>
       </c>
       <c r="P18" t="n">
-        <v>11022144</v>
+        <v>2847149</v>
       </c>
       <c r="Q18" t="n">
-        <v>6460789</v>
+        <v>774634</v>
       </c>
       <c r="R18" t="n">
-        <v>10722048</v>
+        <v>4014404</v>
       </c>
       <c r="S18" t="n">
-        <v>5013047</v>
+        <v>1443480</v>
       </c>
       <c r="T18" t="n">
-        <v>19071874</v>
+        <v>7273226</v>
       </c>
       <c r="U18" t="n">
-        <v>21083239</v>
+        <v>5450960</v>
       </c>
       <c r="V18" t="n">
-        <v>71557</v>
+        <v>3544591</v>
       </c>
       <c r="W18" t="n">
-        <v>53160312</v>
+        <v>17598367</v>
       </c>
       <c r="X18" t="n">
-        <v>3625433</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>19984737</v>
+        <v>7036960</v>
       </c>
       <c r="AA18" t="n">
-        <v>20873148</v>
+        <v>7400151</v>
       </c>
       <c r="AB18" t="n">
-        <v>32287164</v>
+        <v>6461978</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.580840163342067</v>
+        <v>0.3778575942250748</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.2826209031370577</v>
+        <v>0.0400401343562904</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.2138497461487777</v>
+        <v>0.273182748536175</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0457494956638373</v>
+        <v>0.0250140855975329</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0021323437397134</v>
+        <v>0.0002208748252997</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.259599241812615</v>
+        <v>0.2981968341337079</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2370206676331163</v>
+        <v>0.0508831398699632</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.3984123781515316</v>
+        <v>0.1379348759077404</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.3926453253321764</v>
+        <v>0.4205021409088695</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.9543219908272998</v>
+        <v>1.033575009663264</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.5365118390099405</v>
+        <v>0.5704741820331507</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.9091699754456376</v>
+        <v>3.308580127478836</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.1506152136544598</v>
+        <v>0.0360432166465636</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_农夫山泉_2024_年度报告.pdf</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_中国食品_2024_年度报告.pdf</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09633.HK</t>
+          <t>00506.HK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>农夫山泉</t>
+          <t>中国食品</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3143,115 +3143,115 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25622201</v>
+        <v>12278061</v>
       </c>
       <c r="G19" t="n">
-        <v>10165771</v>
+        <v>7602388</v>
       </c>
       <c r="H19" t="n">
-        <v>15456430</v>
+        <v>4675673</v>
       </c>
       <c r="I19" t="n">
-        <v>5010696</v>
+        <v>3235163</v>
       </c>
       <c r="J19" t="n">
-        <v>1067728</v>
+        <v>211245</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>24563</v>
+        <v>1822</v>
       </c>
       <c r="M19" t="n">
-        <v>10058139</v>
+        <v>1356442</v>
       </c>
       <c r="N19" t="n">
-        <v>10033576</v>
+        <v>1357351</v>
       </c>
       <c r="O19" t="n">
-        <v>7622082</v>
+        <v>577845</v>
       </c>
       <c r="P19" t="n">
-        <v>10406067</v>
+        <v>1881448</v>
       </c>
       <c r="Q19" t="n">
-        <v>3566386</v>
+        <v>330845</v>
       </c>
       <c r="R19" t="n">
-        <v>14905813</v>
+        <v>5046875</v>
       </c>
       <c r="S19" t="n">
-        <v>5104288</v>
+        <v>971523</v>
       </c>
       <c r="T19" t="n">
-        <v>26524390</v>
+        <v>8259505</v>
       </c>
       <c r="U19" t="n">
-        <v>23570284</v>
+        <v>5659578</v>
       </c>
       <c r="V19" t="n">
-        <v>161201</v>
+        <v>3552296</v>
       </c>
       <c r="W19" t="n">
-        <v>64393869</v>
+        <v>18749206</v>
       </c>
       <c r="X19" t="n">
-        <v>4419502</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>32135476</v>
+        <v>8223245</v>
       </c>
       <c r="AA19" t="n">
-        <v>33023445</v>
+        <v>8599278</v>
       </c>
       <c r="AB19" t="n">
-        <v>31370424</v>
+        <v>6611848</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.6032436479598299</v>
+        <v>0.3808152606506841</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2974795959176184</v>
+        <v>0.0470632129942993</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.1955607170515913</v>
+        <v>0.2634913607287014</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0416719859468747</v>
+        <v>0.0172050782285574</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.0009586608113799</v>
+        <v>0.0001483947668935</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.237232702998466</v>
+        <v>0.2806964389572588</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1296777696065102</v>
+        <v>0.0317955204326847</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.2394712787421352</v>
+        <v>0.0883972297015426</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.5128352359135309</v>
+        <v>0.4586475821962807</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.8253927839749441</v>
+        <v>1.004409451499986</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.4638429192709017</v>
+        <v>0.6137327782402202</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.365252564850391</v>
+        <v>3.255973487699989</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.139191242781992</v>
+        <v>0.0269460299961044</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
@@ -3260,24 +3260,24 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_农夫山泉_2025_中期报告.pdf</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_中国食品_2025_中期报告.pdf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>09633.HK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Celsius Holdings</t>
+          <t>农夫山泉</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3285,145 +3285,145 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1355630000</v>
+        <v>42895992</v>
       </c>
       <c r="G20" t="n">
-        <v>675423000</v>
+        <v>17980277</v>
       </c>
       <c r="H20" t="n">
-        <v>680207000</v>
+        <v>24915715</v>
       </c>
       <c r="I20" t="n">
-        <v>523479000</v>
+        <v>9173297</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1962470</v>
       </c>
       <c r="K20" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-39322000</v>
+        <v>91469</v>
       </c>
       <c r="M20" t="n">
-        <v>155728000</v>
+        <v>15879327</v>
       </c>
       <c r="N20" t="n">
-        <v>195050000</v>
+        <v>15787858</v>
       </c>
       <c r="O20" t="n">
-        <v>107457000</v>
+        <v>12123304</v>
       </c>
       <c r="P20" t="n">
-        <v>262898000</v>
+        <v>11022144</v>
       </c>
       <c r="Q20" t="n">
-        <v>23390000</v>
+        <v>6460789</v>
       </c>
       <c r="R20" t="n">
-        <v>890190000</v>
+        <v>10722048</v>
       </c>
       <c r="S20" t="n">
-        <v>131165000</v>
+        <v>5013047</v>
       </c>
       <c r="T20" t="n">
-        <v>1324580000</v>
+        <v>19071874</v>
       </c>
       <c r="U20" t="n">
-        <v>55602000</v>
+        <v>21083239</v>
       </c>
       <c r="V20" t="n">
-        <v>12213000</v>
+        <v>71557</v>
       </c>
       <c r="W20" t="n">
-        <v>1766881000</v>
+        <v>53160312</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3625433</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>365535000</v>
+        <v>19984737</v>
       </c>
       <c r="AA20" t="n">
-        <v>542464000</v>
+        <v>20873148</v>
       </c>
       <c r="AB20" t="n">
-        <v>399929000</v>
+        <v>32287164</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5017644932614357</v>
+        <v>0.580840163342067</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0792672041781312</v>
+        <v>0.2826209031370577</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.3861518260882394</v>
+        <v>0.2138497461487777</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.0457494956638373</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.0007376644069547</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.0290064398102727</v>
+        <v>0.0021323437397134</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.3868894904951941</v>
+        <v>0.259599241812615</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.0608173385757161</v>
+        <v>0.2370206676331163</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.2686901925091703</v>
+        <v>0.3984123781515316</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.307017846702749</v>
+        <v>0.3926453253321764</v>
       </c>
       <c r="AM20" t="n">
-        <v>3.623674887493674</v>
+        <v>0.9543219908272998</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.435307152529853</v>
+        <v>0.5365118390099405</v>
       </c>
       <c r="AO20" t="n">
-        <v>2.446541407260578</v>
+        <v>0.9091699754456376</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.0172539704786704</v>
+        <v>0.1506152136544598</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2024年年度报告</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176625000024/celh-20241231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_农夫山泉_2024_年度报告.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>H股</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>09633.HK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Celsius Holdings</t>
+          <t>农夫山泉</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3431,128 +3431,128 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>人民币</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2515269000</v>
+        <v>25622201</v>
       </c>
       <c r="G21" t="n">
-        <v>1247936000</v>
+        <v>10165771</v>
       </c>
       <c r="H21" t="n">
-        <v>1267333000</v>
+        <v>15456430</v>
       </c>
       <c r="I21" t="n">
-        <v>1123871000</v>
+        <v>5010696</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1067728</v>
       </c>
       <c r="K21" t="n">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>16029000</v>
+        <v>24563</v>
       </c>
       <c r="M21" t="n">
-        <v>141062000</v>
+        <v>10058139</v>
       </c>
       <c r="N21" t="n">
-        <v>125033000</v>
+        <v>10033576</v>
       </c>
       <c r="O21" t="n">
-        <v>63837000</v>
+        <v>7622082</v>
       </c>
       <c r="P21" t="n">
-        <v>359442000</v>
+        <v>10406067</v>
       </c>
       <c r="Q21" t="n">
-        <v>36067000</v>
+        <v>3566386</v>
       </c>
       <c r="R21" t="n">
-        <v>398866000</v>
+        <v>14905813</v>
       </c>
       <c r="S21" t="n">
-        <v>337698000</v>
+        <v>5104288</v>
       </c>
       <c r="T21" t="n">
-        <v>1811154000</v>
+        <v>26524390</v>
       </c>
       <c r="U21" t="n">
-        <v>87910000</v>
+        <v>23570284</v>
       </c>
       <c r="V21" t="n">
-        <v>111910000</v>
+        <v>161201</v>
       </c>
       <c r="W21" t="n">
-        <v>5119621000</v>
+        <v>64393869</v>
       </c>
       <c r="X21" t="n">
-        <v>7000000</v>
+        <v>4419502</v>
       </c>
       <c r="Y21" t="n">
-        <v>669926000</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1078726000</v>
+        <v>32135476</v>
       </c>
       <c r="AA21" t="n">
-        <v>2178179000</v>
+        <v>33023445</v>
       </c>
       <c r="AB21" t="n">
-        <v>1181467000</v>
+        <v>31370424</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5038558500104761</v>
+        <v>0.6032436479598299</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.0253797903922005</v>
+        <v>0.2974795959176184</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.4468194057971533</v>
+        <v>0.1955607170515913</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.0416719859468747</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0009541722972770999</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.0063726782304397</v>
+        <v>0.0009586608113799</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.4477735780944304</v>
+        <v>0.237232702998466</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.0124690870671872</v>
+        <v>0.1296777696065102</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.0540319788872647</v>
+        <v>0.2394712787421352</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.4254570797330505</v>
+        <v>0.5128352359135309</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.678975013117325</v>
+        <v>0.8253927839749441</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.369756546147956</v>
+        <v>0.4638429192709017</v>
       </c>
       <c r="AO21" t="n">
-        <v>5.630621739743409</v>
+        <v>1.365252564850391</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.0143392217691229</v>
+        <v>0.139191242781992</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>2025年中期报告</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176626000024/celh-20251231.htm</t>
+          <t>E:\Codex\investment\饮料可比公司研究\raw\official\H股_农夫山泉_2025_中期报告.pdf</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Celsius Holdings</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3581,115 +3581,115 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15351000000</v>
+        <v>1355630000</v>
       </c>
       <c r="G22" t="n">
-        <v>6822000000</v>
+        <v>675423000</v>
       </c>
       <c r="H22" t="n">
-        <v>8529000000</v>
+        <v>680207000</v>
       </c>
       <c r="I22" t="n">
-        <v>5013000000</v>
+        <v>523479000</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>70000000</v>
+        <v>1000000</v>
       </c>
       <c r="L22" t="n">
-        <v>677000000</v>
+        <v>-39322000</v>
       </c>
       <c r="M22" t="n">
-        <v>2591000000</v>
+        <v>155728000</v>
       </c>
       <c r="N22" t="n">
-        <v>1914000000</v>
+        <v>195050000</v>
       </c>
       <c r="O22" t="n">
-        <v>1441000000</v>
+        <v>107457000</v>
       </c>
       <c r="P22" t="n">
-        <v>2219000000</v>
+        <v>262898000</v>
       </c>
       <c r="Q22" t="n">
-        <v>563000000</v>
+        <v>23390000</v>
       </c>
       <c r="R22" t="n">
-        <v>510000000</v>
+        <v>890190000</v>
       </c>
       <c r="S22" t="n">
-        <v>1299000000</v>
+        <v>131165000</v>
       </c>
       <c r="T22" t="n">
-        <v>3997000000</v>
+        <v>1324580000</v>
       </c>
       <c r="U22" t="n">
-        <v>2964000000</v>
+        <v>55602000</v>
       </c>
       <c r="V22" t="n">
-        <v>23634000000</v>
+        <v>12213000</v>
       </c>
       <c r="W22" t="n">
-        <v>53430000000</v>
+        <v>1766881000</v>
       </c>
       <c r="X22" t="n">
-        <v>1026000000</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>12912000000</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8087000000</v>
+        <v>365535000</v>
       </c>
       <c r="AA22" t="n">
-        <v>29187000000</v>
+        <v>542464000</v>
       </c>
       <c r="AB22" t="n">
-        <v>24243000000</v>
+        <v>399929000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.5555989837795583</v>
+        <v>0.5017644932614357</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.0938701061820076</v>
+        <v>0.0792672041781312</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.3265585303888997</v>
+        <v>0.3861518260882394</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.0045599635202918</v>
+        <v>0.0007376644069547</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.0441013614748224</v>
+        <v>-0.0290064398102727</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.3311184939091915</v>
+        <v>0.3868894904951941</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.0269698671158525</v>
+        <v>0.0608173385757161</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.0594398383038402</v>
+        <v>0.2686901925091703</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.5462661426165076</v>
+        <v>0.307017846702749</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.4942500309138123</v>
+        <v>3.623674887493674</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.0630641770743168</v>
+        <v>2.435307152529853</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.539902845246357</v>
+        <v>2.446541407260578</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.0366751351703472</v>
+        <v>0.0172539704786704</v>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813525000013/kdp-20241231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176625000024/celh-20241231.htm</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Celsius Holdings</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -3727,115 +3727,115 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>16603000000</v>
+        <v>2515269000</v>
       </c>
       <c r="G23" t="n">
-        <v>7604000000</v>
+        <v>1247936000</v>
       </c>
       <c r="H23" t="n">
-        <v>8999000000</v>
+        <v>1267333000</v>
       </c>
       <c r="I23" t="n">
-        <v>5351000000</v>
+        <v>1123871000</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>70000000</v>
+        <v>2400000</v>
       </c>
       <c r="L23" t="n">
-        <v>888000000</v>
+        <v>16029000</v>
       </c>
       <c r="M23" t="n">
-        <v>3575000000</v>
+        <v>141062000</v>
       </c>
       <c r="N23" t="n">
-        <v>2687000000</v>
+        <v>125033000</v>
       </c>
       <c r="O23" t="n">
-        <v>2079000000</v>
+        <v>63837000</v>
       </c>
       <c r="P23" t="n">
-        <v>1991000000</v>
+        <v>359442000</v>
       </c>
       <c r="Q23" t="n">
-        <v>486000000</v>
+        <v>36067000</v>
       </c>
       <c r="R23" t="n">
-        <v>1026000000</v>
+        <v>398866000</v>
       </c>
       <c r="S23" t="n">
-        <v>1733000000</v>
+        <v>337698000</v>
       </c>
       <c r="T23" t="n">
-        <v>5266000000</v>
+        <v>1811154000</v>
       </c>
       <c r="U23" t="n">
-        <v>3230000000</v>
+        <v>87910000</v>
       </c>
       <c r="V23" t="n">
-        <v>23725000000</v>
+        <v>111910000</v>
       </c>
       <c r="W23" t="n">
-        <v>55459000000</v>
+        <v>5119621000</v>
       </c>
       <c r="X23" t="n">
-        <v>895000000</v>
+        <v>7000000</v>
       </c>
       <c r="Y23" t="n">
-        <v>13036000000</v>
+        <v>669926000</v>
       </c>
       <c r="Z23" t="n">
-        <v>8290000000</v>
+        <v>1078726000</v>
       </c>
       <c r="AA23" t="n">
-        <v>29943000000</v>
+        <v>2178179000</v>
       </c>
       <c r="AB23" t="n">
-        <v>25516000000</v>
+        <v>1181467000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.5420104800337289</v>
+        <v>0.5038558500104761</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.1252183340360176</v>
+        <v>0.0253797903922005</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.3222911522014093</v>
+        <v>0.4468194057971533</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.0042161055230982</v>
+        <v>0.0009541722972770999</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.0534843100644461</v>
+        <v>0.0063726782304397</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.3265072577245076</v>
+        <v>0.4477735780944304</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0374871526713428</v>
+        <v>0.0124690870671872</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.0814782881329362</v>
+        <v>0.0540319788872647</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.539912367695054</v>
+        <v>0.4254570797330505</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.6352231604342582</v>
+        <v>1.678975013117325</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.1237635705669481</v>
+        <v>0.369756546147956</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.9576719576719576</v>
+        <v>5.630621739743409</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.029271818346082</v>
+        <v>0.0143392217691229</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813526000016/kdp-20251231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1341766/000134176626000024/celh-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3873,115 +3873,115 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>47061000000</v>
+        <v>15351000000</v>
       </c>
       <c r="G24" t="n">
-        <v>18324000000</v>
+        <v>6822000000</v>
       </c>
       <c r="H24" t="n">
-        <v>28737000000</v>
+        <v>8529000000</v>
       </c>
       <c r="I24" t="n">
-        <v>14582000000</v>
+        <v>5013000000</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>70000000</v>
       </c>
       <c r="L24" t="n">
-        <v>-3094000000</v>
+        <v>677000000</v>
       </c>
       <c r="M24" t="n">
-        <v>9992000000</v>
+        <v>2591000000</v>
       </c>
       <c r="N24" t="n">
-        <v>13086000000</v>
+        <v>1914000000</v>
       </c>
       <c r="O24" t="n">
-        <v>10631000000</v>
+        <v>1441000000</v>
       </c>
       <c r="P24" t="n">
-        <v>6805000000</v>
+        <v>2219000000</v>
       </c>
       <c r="Q24" t="n">
-        <v>2064000000</v>
+        <v>563000000</v>
       </c>
       <c r="R24" t="n">
-        <v>10828000000</v>
+        <v>510000000</v>
       </c>
       <c r="S24" t="n">
-        <v>4728000000</v>
+        <v>1299000000</v>
       </c>
       <c r="T24" t="n">
-        <v>25997000000</v>
+        <v>3997000000</v>
       </c>
       <c r="U24" t="n">
-        <v>10303000000</v>
+        <v>2964000000</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>23634000000</v>
       </c>
       <c r="W24" t="n">
-        <v>100549000000</v>
+        <v>53430000000</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1026000000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>12912000000</v>
       </c>
       <c r="Z24" t="n">
-        <v>25249000000</v>
+        <v>8087000000</v>
       </c>
       <c r="AA24" t="n">
-        <v>75693000000</v>
+        <v>29187000000</v>
       </c>
       <c r="AB24" t="n">
-        <v>24856000000</v>
+        <v>24243000000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6106330082233696</v>
+        <v>0.5555989837795583</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.225898302203523</v>
+        <v>0.0938701061820076</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.3098531692909202</v>
+        <v>0.3265585303888997</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.0045599635202918</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.0657444593187565</v>
+        <v>0.0441013614748224</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.3098531692909202</v>
+        <v>0.3311184939091915</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1057295447990532</v>
+        <v>0.0269698671158525</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.4277035725780496</v>
+        <v>0.0594398383038402</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.7527971436811902</v>
+        <v>0.5462661426165076</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.029624935641015</v>
+        <v>0.4942500309138123</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.4288486672739514</v>
+        <v>0.0630641770743168</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.640109114852789</v>
+        <v>1.539902845246357</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.0438579715688149</v>
+        <v>0.0366751351703472</v>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/21344/000002134425000011/ko-20241231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813525000013/kdp-20241231.htm</t>
         </is>
       </c>
     </row>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4019,115 +4019,115 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>47941000000</v>
+        <v>16603000000</v>
       </c>
       <c r="G25" t="n">
-        <v>18397000000</v>
+        <v>7604000000</v>
       </c>
       <c r="H25" t="n">
-        <v>29544000000</v>
+        <v>8999000000</v>
       </c>
       <c r="I25" t="n">
-        <v>14521000000</v>
+        <v>5351000000</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>70000000</v>
       </c>
       <c r="L25" t="n">
-        <v>-2236000000</v>
+        <v>888000000</v>
       </c>
       <c r="M25" t="n">
-        <v>13762000000</v>
+        <v>3575000000</v>
       </c>
       <c r="N25" t="n">
-        <v>15998000000</v>
+        <v>2687000000</v>
       </c>
       <c r="O25" t="n">
-        <v>13107000000</v>
+        <v>2079000000</v>
       </c>
       <c r="P25" t="n">
-        <v>7408000000</v>
+        <v>1991000000</v>
       </c>
       <c r="Q25" t="n">
-        <v>2112000000</v>
+        <v>486000000</v>
       </c>
       <c r="R25" t="n">
-        <v>10270000000</v>
+        <v>1026000000</v>
       </c>
       <c r="S25" t="n">
-        <v>4425000000</v>
+        <v>1733000000</v>
       </c>
       <c r="T25" t="n">
-        <v>31044000000</v>
+        <v>5266000000</v>
       </c>
       <c r="U25" t="n">
-        <v>9613000000</v>
+        <v>3230000000</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>23725000000</v>
       </c>
       <c r="W25" t="n">
-        <v>104816000000</v>
+        <v>55459000000</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>895000000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>13036000000</v>
       </c>
       <c r="Z25" t="n">
-        <v>21281000000</v>
+        <v>8290000000</v>
       </c>
       <c r="AA25" t="n">
-        <v>72647000000</v>
+        <v>29943000000</v>
       </c>
       <c r="AB25" t="n">
-        <v>32169000000</v>
+        <v>25516000000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.6162574831563797</v>
+        <v>0.5420104800337289</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.2733985523873094</v>
+        <v>0.1252183340360176</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.302893139483949</v>
+        <v>0.3222911522014093</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.0042161055230982</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.0466406624809661</v>
+        <v>0.0534843100644461</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.302893139483949</v>
+        <v>0.3265072577245076</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.1250477026408182</v>
+        <v>0.0374871526713428</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.4074419472162641</v>
+        <v>0.0814782881329362</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.6930907495038925</v>
+        <v>0.539912367695054</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.458766035430666</v>
+        <v>0.6352231604342582</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.4825901038485033</v>
+        <v>0.1237635705669481</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.5651941710536355</v>
+        <v>0.9576719576719576</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.0440541498925762</v>
+        <v>0.029271818346082</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/21344/000162828026010047/ko-20251231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1418135/000141813526000016/kdp-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7492709000</v>
+        <v>47061000000</v>
       </c>
       <c r="G26" t="n">
-        <v>3443831000</v>
+        <v>18324000000</v>
       </c>
       <c r="H26" t="n">
-        <v>4048878000</v>
+        <v>28737000000</v>
       </c>
       <c r="I26" t="n">
-        <v>2118584000</v>
+        <v>14582000000</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -4183,64 +4183,64 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>-59165000</v>
+        <v>-3094000000</v>
       </c>
       <c r="M26" t="n">
-        <v>1930294000</v>
+        <v>9992000000</v>
       </c>
       <c r="N26" t="n">
-        <v>1989459000</v>
+        <v>13086000000</v>
       </c>
       <c r="O26" t="n">
-        <v>1509048000</v>
+        <v>10631000000</v>
       </c>
       <c r="P26" t="n">
-        <v>1928533000</v>
+        <v>6805000000</v>
       </c>
       <c r="Q26" t="n">
-        <v>264074000</v>
+        <v>2064000000</v>
       </c>
       <c r="R26" t="n">
-        <v>1533287000</v>
+        <v>10828000000</v>
       </c>
       <c r="S26" t="n">
-        <v>737107000</v>
+        <v>4728000000</v>
       </c>
       <c r="T26" t="n">
-        <v>3641504000</v>
+        <v>25997000000</v>
       </c>
       <c r="U26" t="n">
-        <v>1047024000</v>
+        <v>10303000000</v>
       </c>
       <c r="V26" t="n">
-        <v>1414252000</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>7719089000</v>
+        <v>100549000000</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>373951000</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1097519000</v>
+        <v>25249000000</v>
       </c>
       <c r="AA26" t="n">
-        <v>1761371000</v>
+        <v>75693000000</v>
       </c>
       <c r="AB26" t="n">
-        <v>5957718000</v>
+        <v>24856000000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.54037571724726</v>
+        <v>0.6106330082233696</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.2014021897820935</v>
+        <v>0.225898302203523</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2827527400303415</v>
+        <v>0.3098531692909202</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -4249,31 +4249,31 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.0078963429648742</v>
+        <v>-0.0657444593187565</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.2827527400303415</v>
+        <v>0.3098531692909202</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.1954956083548201</v>
+        <v>0.1057295447990532</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.2532929554571062</v>
+        <v>0.4277035725780496</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.2281837921547478</v>
+        <v>0.7527971436811902</v>
       </c>
       <c r="AM26" t="n">
-        <v>3.317941648390597</v>
+        <v>1.029624935641015</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.397048251556465</v>
+        <v>0.4288486672739514</v>
       </c>
       <c r="AO26" t="n">
-        <v>1.277979891958374</v>
+        <v>0.640109114852789</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.0352441286589403</v>
+        <v>0.0438579715688149</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/865752/000141057825000248/mnst-20241231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/21344/000002134425000011/ko-20241231.htm</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -4311,16 +4311,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8294343000</v>
+        <v>47941000000</v>
       </c>
       <c r="G27" t="n">
-        <v>3662148000</v>
+        <v>18397000000</v>
       </c>
       <c r="H27" t="n">
-        <v>4632195000</v>
+        <v>29544000000</v>
       </c>
       <c r="I27" t="n">
-        <v>2212841000</v>
+        <v>14521000000</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -4329,64 +4329,64 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-63175000</v>
+        <v>-2236000000</v>
       </c>
       <c r="M27" t="n">
-        <v>2419354000</v>
+        <v>13762000000</v>
       </c>
       <c r="N27" t="n">
-        <v>2482529000</v>
+        <v>15998000000</v>
       </c>
       <c r="O27" t="n">
-        <v>1905432000</v>
+        <v>13107000000</v>
       </c>
       <c r="P27" t="n">
-        <v>2098177000</v>
+        <v>7408000000</v>
       </c>
       <c r="Q27" t="n">
-        <v>132275000</v>
+        <v>2112000000</v>
       </c>
       <c r="R27" t="n">
-        <v>2088117000</v>
+        <v>10270000000</v>
       </c>
       <c r="S27" t="n">
-        <v>799623000</v>
+        <v>4425000000</v>
       </c>
       <c r="T27" t="n">
-        <v>5361084000</v>
+        <v>31044000000</v>
       </c>
       <c r="U27" t="n">
-        <v>1081544000</v>
+        <v>9613000000</v>
       </c>
       <c r="V27" t="n">
-        <v>1379268000</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>9988945000</v>
+        <v>104816000000</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>373951000</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1447780000</v>
+        <v>21281000000</v>
       </c>
       <c r="AA27" t="n">
-        <v>1734837000</v>
+        <v>72647000000</v>
       </c>
       <c r="AB27" t="n">
-        <v>8254108000</v>
+        <v>32169000000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.5584764218214752</v>
+        <v>0.6162574831563797</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.2297266944470466</v>
+        <v>0.2733985523873094</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2667891839052231</v>
+        <v>0.302893139483949</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4395,31 +4395,31 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.0076166370259826</v>
+        <v>-0.0466406624809661</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.2667891839052231</v>
+        <v>0.302893139483949</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.1907540786339298</v>
+        <v>0.1250477026408182</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.230846506975678</v>
+        <v>0.4074419472162641</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.1736756984846748</v>
+        <v>0.6930907495038925</v>
       </c>
       <c r="AM27" t="n">
-        <v>3.702968683087209</v>
+        <v>1.458766035430666</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.442288883670171</v>
+        <v>0.4825901038485033</v>
       </c>
       <c r="AO27" t="n">
-        <v>1.101155538481562</v>
+        <v>0.5651941710536355</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.0159476163452608</v>
+        <v>0.0440541498925762</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/865752/000110465926020831/mnst-20251231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/21344/000162828026010047/ko-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4457,115 +4457,115 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>91854000000</v>
+        <v>7492709000</v>
       </c>
       <c r="G28" t="n">
-        <v>41744000000</v>
+        <v>3443831000</v>
       </c>
       <c r="H28" t="n">
-        <v>50110000000</v>
+        <v>4048878000</v>
       </c>
       <c r="I28" t="n">
-        <v>37190000000</v>
+        <v>2118584000</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>813000000</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>941000000</v>
+        <v>-59165000</v>
       </c>
       <c r="M28" t="n">
-        <v>12887000000</v>
+        <v>1930294000</v>
       </c>
       <c r="N28" t="n">
-        <v>11946000000</v>
+        <v>1989459000</v>
       </c>
       <c r="O28" t="n">
-        <v>9578000000</v>
+        <v>1509048000</v>
       </c>
       <c r="P28" t="n">
-        <v>12507000000</v>
+        <v>1928533000</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>264074000</v>
       </c>
       <c r="R28" t="n">
-        <v>8505000000</v>
+        <v>1533287000</v>
       </c>
       <c r="S28" t="n">
-        <v>5306000000</v>
+        <v>737107000</v>
       </c>
       <c r="T28" t="n">
-        <v>25826000000</v>
+        <v>3641504000</v>
       </c>
       <c r="U28" t="n">
-        <v>28008000000</v>
+        <v>1047024000</v>
       </c>
       <c r="V28" t="n">
-        <v>1102000000</v>
+        <v>1414252000</v>
       </c>
       <c r="W28" t="n">
-        <v>99467000000</v>
+        <v>7719089000</v>
       </c>
       <c r="X28" t="n">
-        <v>7082000000</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>37224000000</v>
+        <v>373951000</v>
       </c>
       <c r="Z28" t="n">
-        <v>31536000000</v>
+        <v>1097519000</v>
       </c>
       <c r="AA28" t="n">
-        <v>81296000000</v>
+        <v>1761371000</v>
       </c>
       <c r="AB28" t="n">
-        <v>18041000000</v>
+        <v>5957718000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.5455396607659982</v>
+        <v>0.54037571724726</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.1042741742330219</v>
+        <v>0.2014021897820935</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.4048816600256929</v>
+        <v>0.2827527400303415</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.008851002678163101</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.0102445184749711</v>
+        <v>-0.0078963429648742</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.4137326627038561</v>
+        <v>0.2827527400303415</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.09629324298511061</v>
+        <v>0.1954956083548201</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.5309018347098277</v>
+        <v>0.2532929554571062</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.8173162958569173</v>
+        <v>0.2281837921547478</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.8189370877727042</v>
+        <v>3.317941648390597</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.2696917808219178</v>
+        <v>1.397048251556465</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.30580496972228</v>
+        <v>1.277979891958374</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.0352441286589403</v>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/77476/000007747625000007/pep-20241228.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/865752/000141057825000248/mnst-20241231x10k.htm</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4603,122 +4603,414 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>8294343000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3662148000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4632195000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2212841000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-63175000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2419354000</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2482529000</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1905432000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2098177000</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>132275000</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2088117000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>799623000</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5361084000</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1081544000</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1379268000</v>
+      </c>
+      <c r="W29" t="n">
+        <v>9988945000</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>373951000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1447780000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1734837000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>8254108000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.5584764218214752</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.2297266944470466</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.2667891839052231</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>-0.0076166370259826</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.2667891839052231</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.1907540786339298</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.230846506975678</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.1736756984846748</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>3.702968683087209</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.442288883670171</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1.101155538481562</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.0159476163452608</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/865752/000110465926020831/mnst-20251231x10k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>91854000000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>41744000000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>50110000000</v>
+      </c>
+      <c r="I30" t="n">
+        <v>37190000000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>813000000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>941000000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12887000000</v>
+      </c>
+      <c r="N30" t="n">
+        <v>11946000000</v>
+      </c>
+      <c r="O30" t="n">
+        <v>9578000000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>12507000000</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>8505000000</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5306000000</v>
+      </c>
+      <c r="T30" t="n">
+        <v>25826000000</v>
+      </c>
+      <c r="U30" t="n">
+        <v>28008000000</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1102000000</v>
+      </c>
+      <c r="W30" t="n">
+        <v>99467000000</v>
+      </c>
+      <c r="X30" t="n">
+        <v>7082000000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>37224000000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>31536000000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>81296000000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>18041000000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.5455396607659982</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.1042741742330219</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.4048816600256929</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.008851002678163101</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.0102445184749711</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.4137326627038561</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.09629324298511061</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.5309018347098277</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.8173162958569173</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.8189370877727042</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.2696917808219178</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1.30580496972228</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/77476/000007747625000007/pep-20241228.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>93925000000</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G31" t="n">
         <v>43066000000</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H31" t="n">
         <v>50859000000</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I31" t="n">
         <v>37368000000</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>839000000</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L31" t="n">
         <v>1254000000</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M31" t="n">
         <v>11498000000</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N31" t="n">
         <v>10244000000</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O31" t="n">
         <v>8240000000</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P31" t="n">
         <v>12087000000</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>9159000000</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S31" t="n">
         <v>5845000000</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T31" t="n">
         <v>27949000000</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U31" t="n">
         <v>29905000000</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V31" t="n">
         <v>500000000</v>
       </c>
-      <c r="W29" t="n">
+      <c r="W31" t="n">
         <v>107399000000</v>
       </c>
-      <c r="X29" t="n">
+      <c r="X31" t="n">
         <v>6861000000</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y31" t="n">
         <v>42321000000</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="Z31" t="n">
         <v>32764000000</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AA31" t="n">
         <v>86852000000</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AB31" t="n">
         <v>20406000000</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AC31" t="n">
         <v>0.541485227575193</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AD31" t="n">
         <v>0.0877295714665956</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE31" t="n">
         <v>0.3978493478839499</v>
       </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
         <v>0.0089326590364652</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH31" t="n">
         <v>0.0133510779877561</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AI31" t="n">
         <v>0.4067820069204152</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AJ31" t="n">
         <v>0.0767232469576066</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AK31" t="n">
         <v>0.4038028030971283</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AL31" t="n">
         <v>0.8086853695099582</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AM31" t="n">
         <v>0.8530399218654621</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AN31" t="n">
         <v>0.2795446221462581</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AO31" t="n">
         <v>1.466868932038835</v>
       </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="inlineStr">
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="AR29" t="inlineStr">
+      <c r="AR31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/77476/000007747626000007/pep-20251227.htm</t>
         </is>
